--- a/dietitian_forms/023_diet_plan_update_communication_form--dietitian_forms.xlsx
+++ b/dietitian_forms/023_diet_plan_update_communication_form--dietitian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>updated_diet_plan</t>
+          <t>updated_diet_plan_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>updated_dietician_phone</t>
+          <t>updated_dietician_phone_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Updated Dician Phone</t>
+          <t>Updated Dietician Phone 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>updated_dietician_email</t>
+          <t>updated_dietician_email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Updated Dician Email</t>
+          <t>Updated Dietician Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>updated_dietician_address</t>
+          <t>updated_dietician_address_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Updated Dician Address</t>
+          <t>Updated Dietician Address 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>next_meeting_time</t>
+          <t>next_meeting_time_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Next Meeting Time</t>
+          <t>Next Meeting Time 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>next_meeting_date</t>
+          <t>next_meeting_date_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Next Meeting Date</t>
+          <t>Next Meeting Date 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>next_meeting_place</t>
+          <t>next_meeting_place_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Next Meeting Place</t>
+          <t>Next Meeting Place 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>updated_diet_plan_choices</t>
+          <t>updated_diet_plan_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>updated_diet_plan_choices</t>
+          <t>updated_diet_plan_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>updated_diet_plan_choices</t>
+          <t>updated_diet_plan_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
